--- a/full_report_GPT-5.5_FUNC-004.xlsx
+++ b/full_report_GPT-5.5_FUNC-004.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>系统提示词失败：('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))；('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>系统提示词失败：404 Client Error: Not Found for url: https://99887123.xyz/v1/chat/completions；404 Client Error: Not Found for url: https://99887123.xyz/v1/chat/completions</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
